--- a/src/test/resources/testData.xlsx
+++ b/src/test/resources/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sachin\eclipse-workspace\Flight_Booking\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{17AD43C5-6106-4A35-A2BB-FBFAC6B4E6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB640630-ADC4-421E-858C-D8C90ABCF12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{5EC24417-0512-4E53-A015-570A550DCF64}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8880" xr2:uid="{5EC24417-0512-4E53-A015-570A550DCF64}"/>
   </bookViews>
   <sheets>
     <sheet name="testData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>fromCity</t>
   </si>
@@ -59,12 +59,6 @@
   </si>
   <si>
     <t>London</t>
-  </si>
-  <si>
-    <t>Sachin</t>
-  </si>
-  <si>
-    <t>Gautam Nagar</t>
   </si>
   <si>
     <t>Bhopal</t>
@@ -978,21 +972,6 @@
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2">
-        <v>462023</v>
-      </c>
       <c r="H2" s="1">
         <v>1234567890123450</v>
       </c>
@@ -1003,27 +982,27 @@
         <v>2028</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>462021</v>
@@ -1038,7 +1017,7 @@
         <v>2029</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
